--- a/data/digital-nomad-cities.xlsx
+++ b/data/digital-nomad-cities.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="综合数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="按区域" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="专题排行" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="签证政策" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="按身份推荐" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="数据说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按区域" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专题排行" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="签证政策" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按身份推荐" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'综合数据'!$A$4:$X$68</definedName>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -607,11 +607,10 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>覆盖 5 大区域 / 39 国家 / 64 城市 · 数据综合自 Nomad List 等主流数字游民社区 · 评分 0–10 分制（10 最佳）· 月成本为单人月支出中位数（USD）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>覆盖 5 大区域 / 40 国家 / 80 城市 · 数据综合自 Nomad List 等主流数字游民社区 · 评分 0–10 分制（10 最佳）· 月成本为单人月支出中位数（USD）</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -1240,91 +1239,91 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>拉斯帕尔马斯</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🇪🇸</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2200</v>
+        <v>5000</v>
       </c>
       <c r="H10" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>全年</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>西班牙数字游民</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1343,29 +1342,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>塔林</t>
+          <t>拉斯帕尔马斯</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>爱沙尼亚</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🇪🇪</t>
+          <t>🇪🇸</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="H11" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1373,22 +1372,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
         <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
         <v>8</v>
@@ -1397,28 +1396,28 @@
         <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6月-8月</t>
+          <t>全年</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>数字游民签证</t>
+          <t>西班牙数字游民</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -1441,29 +1440,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>布拉格</t>
+          <t>塔林</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>爱沙尼亚</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🇨🇿</t>
+          <t>🇪🇪</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1471,16 +1470,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
         <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N12" t="n">
         <v>7</v>
@@ -1489,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
         <v>8</v>
@@ -1498,25 +1497,25 @@
         <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5月-9月</t>
+          <t>6月-8月</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>捷克游民签</t>
+          <t>数字游民签证</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -1539,29 +1538,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>波尔图</t>
+          <t>布拉格</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🇵🇹</t>
+          <t>🇨🇿</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="H13" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1569,44 +1568,44 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K13" t="n">
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" t="n">
         <v>9</v>
       </c>
-      <c r="R13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>16</v>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>5月-9月</t>
@@ -1614,11 +1613,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>D7/D8</t>
+          <t>捷克游民签</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1632,91 +1631,91 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>巴塞罗那</t>
+          <t>大理</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🇪🇸</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="H14" t="n">
-        <v>2400</v>
+        <v>850</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M14" t="n">
         <v>9</v>
       </c>
-      <c r="M14" t="n">
-        <v>7</v>
-      </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
         <v>8</v>
       </c>
       <c r="R14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="V14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5月-6月, 9月-10月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>西班牙数字游民签证</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1735,29 +1734,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>布达佩斯</t>
+          <t>波尔图</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>匈牙利</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🇭🇺</t>
+          <t>🇵🇹</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1700</v>
+        <v>1300</v>
       </c>
       <c r="H15" t="n">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1765,52 +1764,52 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
         <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
         <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
         <v>7</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4月-6月, 9月-10月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>白卡/游民签</t>
+          <t>D7/D8</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -1833,29 +1832,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>克拉科夫</t>
+          <t>巴塞罗那</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🇵🇱</t>
+          <t>🇪🇸</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1400</v>
+        <v>2500</v>
       </c>
       <c r="H16" t="n">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1863,16 +1862,16 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>7</v>
@@ -1881,38 +1880,38 @@
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
         <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5月-9月</t>
+          <t>5月-6月, 9月-10月</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>波兰游民签</t>
+          <t>西班牙数字游民签证</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -1931,29 +1930,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>马德拉</t>
+          <t>布达佩斯</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>匈牙利</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🇵🇹</t>
+          <t>🇭🇺</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1100</v>
+        <v>1700</v>
       </c>
       <c r="H17" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1961,25 +1960,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="K17" t="n">
         <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>8</v>
@@ -1988,29 +1987,29 @@
         <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3月-10月</t>
+          <t>4月-6月, 9月-10月</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>D7/D8</t>
+          <t>白卡/游民签</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2024,34 +2023,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中东</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>迪拜</t>
+          <t>克拉科夫</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>阿联酋</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🇦🇪</t>
+          <t>🇵🇱</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="H18" t="n">
-        <v>3200</v>
+        <v>1300</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2059,56 +2058,56 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" t="n">
         <v>9</v>
       </c>
-      <c r="K18" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>30</v>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>11月-3月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>旅游签/虚拟办公</t>
+          <t>波兰游民签</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2127,86 +2126,86 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>首尔</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🇰🇷</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1300</v>
+        <v>3500</v>
       </c>
       <c r="H19" t="n">
-        <v>2200</v>
+        <v>1450</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
         <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4月-6月, 9月-10月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>免签/创业签</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2220,34 +2219,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>墨西哥城</t>
+          <t>马德拉</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇵🇹</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="H20" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2255,56 +2254,56 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>6</v>
-      </c>
       <c r="N20" t="n">
         <v>7</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3月-5月, 10月-11月</t>
+          <t>3月-10月</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>临时居留6月</t>
+          <t>D7/D8</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2318,34 +2317,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>中东</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>布宜诺斯艾利斯</t>
+          <t>迪拜</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>阿联酋</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🇦🇷</t>
+          <t>🇦🇪</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3000</v>
+        <v>1900</v>
       </c>
       <c r="H21" t="n">
-        <v>1100</v>
+        <v>3200</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2353,56 +2352,56 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
         <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9月-12月, 3月-4月</t>
+          <t>11月-3月</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>数字游民签</t>
+          <t>旅游签/虚拟办公</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2416,91 +2415,91 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>斯普利特</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>克罗地亚</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>🇭🇷</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="H22" t="n">
         <v>1500</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V22" t="n">
         <v>17</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5月-9月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Croatia游民签/申根</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2514,91 +2513,91 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>特内里费</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>🇪🇸</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1300</v>
+        <v>4000</v>
       </c>
       <c r="H23" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="M23" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Q23" t="n">
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>全年</t>
+          <t>10月-4月</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>西班牙数字游民</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2617,86 +2616,86 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>巴厘岛 (长谷)</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>印尼</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>🇮🇩</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5800</v>
+        <v>4500</v>
       </c>
       <c r="H24" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7</v>
-      </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4月-10月</t>
+          <t>4月-6月, 9月-10月</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B211A 6月/VOA</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2710,91 +2709,91 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>麦德林</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>🇨🇴</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="H25" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="K25" t="n">
+        <v>7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" t="n">
         <v>9</v>
       </c>
-      <c r="L25" t="n">
-        <v>8</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6</v>
-      </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>7</v>
       </c>
       <c r="T25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="V25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>12月-3月, 7月-8月</t>
+          <t>10月-4月</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>游民签M</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2808,91 +2807,91 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>蒙得维的亚</t>
+          <t>阳朔</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>乌拉圭</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>🇺🇾</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
         <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="U26" t="n">
         <v>8</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>11月-3月</t>
+          <t>4月-10月</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>游民友好</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2911,29 +2910,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>清迈</t>
+          <t>首尔</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>🇹🇭</t>
+          <t>🇰🇷</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4500</v>
+        <v>1300</v>
       </c>
       <c r="H27" t="n">
-        <v>850</v>
+        <v>2200</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2941,56 +2940,56 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8</v>
+      </c>
+      <c r="M27" t="n">
         <v>9</v>
       </c>
-      <c r="L27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" t="n">
-        <v>8.5</v>
-      </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27" t="n">
         <v>7</v>
       </c>
       <c r="V27" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>11月-2月</t>
+          <t>4月-6月, 9月-10月</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>DTV 5年/教育签证</t>
+          <t>免签/创业签</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3004,34 +3003,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>曼谷</t>
+          <t>墨西哥城</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>🇹🇭</t>
+          <t>🇲🇽</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="H28" t="n">
-        <v>1150</v>
+        <v>1500</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3039,34 +3038,34 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
         <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
         <v>5</v>
@@ -3075,20 +3074,20 @@
         <v>7</v>
       </c>
       <c r="V28" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>11月-2月</t>
+          <t>3月-5月, 10月-11月</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>DTV/教育签证</t>
+          <t>临时居留6月</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3102,31 +3101,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>第比利斯</t>
+          <t>布宜诺斯艾利斯</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>🇬🇪</t>
+          <t>🇦🇷</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H29" t="n">
         <v>1100</v>
@@ -3137,56 +3136,56 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>7</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29" t="n">
         <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>5月-10月</t>
+          <t>9月-12月, 3月-4月</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>免签1年</t>
+          <t>数字游民签</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3200,91 +3199,91 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中东</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>阿布扎比</t>
+          <t>三亚</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>阿联酋</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>🇦🇪</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="H30" t="n">
-        <v>3100</v>
+        <v>2000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="L30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
         <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
         <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V30" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>11月-3月</t>
+          <t>10月-4月</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>旅游签</t>
+          <t>国内无需签证/海南30天免签(59国)</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3298,34 +3297,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>普吉</t>
+          <t>斯普利特</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>克罗地亚</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>🇹🇭</t>
+          <t>🇭🇷</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="H31" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3333,56 +3332,56 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>7</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
         <v>7</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U31" t="n">
         <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>11月-4月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>DTV 5年</t>
+          <t>Croatia游民签/申根</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3396,34 +3395,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>苏梅岛</t>
+          <t>特内里费</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>🇹🇭</t>
+          <t>🇪🇸</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="H32" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3431,34 +3430,34 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
         <v>8</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
         <v>7</v>
@@ -3467,20 +3466,20 @@
         <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>12月-4月</t>
+          <t>全年</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>DTV 5年</t>
+          <t>西班牙数字游民</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3499,86 +3498,86 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>胡志明市</t>
+          <t>安吉</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>🇻🇳</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="H33" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L33" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M33" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="O33" t="n">
-        <v>6</v>
-      </c>
-      <c r="P33" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6</v>
-      </c>
-      <c r="S33" t="n">
-        <v>7</v>
-      </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="U33" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="V33" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>12月-4月</t>
+          <t>4月-6月, 9月-11月</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>电子签/免签45天</t>
+          <t>国内无需签证/240h免签过境(杭州入境)</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3592,91 +3591,91 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>班斯科</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>🇧🇬</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1500</v>
       </c>
       <c r="H34" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P34" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R34" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="T34" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>6月-9月, 12月-3月滑雪</t>
+          <t>全年</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>保加利亚游民签</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3690,91 +3689,91 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>希腊</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>🇬🇷</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="H35" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K35" t="n">
         <v>6.5</v>
       </c>
-      <c r="K35" t="n">
-        <v>7</v>
-      </c>
       <c r="L35" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
         <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>4月-6月, 9月-10月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>希腊游民签</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3788,91 +3787,91 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>圣米格尔</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="H36" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
         <v>8</v>
       </c>
       <c r="R36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U36" t="n">
         <v>7</v>
       </c>
       <c r="V36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>10月-5月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>临时居留</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3886,34 +3885,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>弗洛里亚诺波利斯</t>
+          <t>巴厘岛 (长谷)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印尼</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>🇧🇷</t>
+          <t>🇮🇩</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1100</v>
+        <v>5800</v>
       </c>
       <c r="H37" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3921,56 +3920,56 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="L37" t="n">
         <v>7</v>
       </c>
       <c r="M37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
         <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>12月-3月</t>
+          <t>4月-10月</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>数字游民签</t>
+          <t>B211A 6月/VOA</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3984,34 +3983,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>槟城</t>
+          <t>麦德林</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>🇲🇾</t>
+          <t>🇨🇴</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1300</v>
+        <v>4200</v>
       </c>
       <c r="H38" t="n">
-        <v>950</v>
+        <v>1200</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4019,56 +4018,56 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
         <v>7</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38" t="n">
         <v>7</v>
       </c>
       <c r="V38" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>12月-2月</t>
+          <t>12月-3月, 7月-8月</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>DE R passes</t>
+          <t>游民签M</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -4082,34 +4081,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>索菲亚</t>
+          <t>蒙得维的亚</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>乌拉圭</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>🇧🇬</t>
+          <t>🇺🇾</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4117,10 +4116,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
         <v>6</v>
@@ -4129,19 +4128,19 @@
         <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4150,23 +4149,23 @@
         <v>7</v>
       </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>5月-9月</t>
+          <t>11月-3月</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>保加利亚游民签</t>
+          <t>游民友好</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -4180,69 +4179,69 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>瓦哈卡</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="H40" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="K40" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
         <v>7</v>
@@ -4251,20 +4250,20 @@
         <v>7</v>
       </c>
       <c r="V40" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>10月-5月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>临时居留</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -4278,91 +4277,91 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>巴拿马城</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>巴拿马</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>🇵🇦</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="H41" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K41" t="n">
         <v>7</v>
       </c>
       <c r="L41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U41" t="n">
         <v>7</v>
       </c>
       <c r="V41" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>12月-3月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>游民签/短租友好</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -4381,86 +4380,86 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>河内</t>
+          <t>丽江</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>🇻🇳</t>
+          <t>🇨🇳</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="H42" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>美元</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="J42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K42" t="n">
         <v>6.5</v>
       </c>
-      <c r="K42" t="n">
-        <v>8</v>
-      </c>
       <c r="L42" t="n">
         <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="U42" t="n">
         <v>7</v>
       </c>
       <c r="V42" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>10月-12月</t>
+          <t>3月-5月, 9月-11月</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>电子签</t>
+          <t>国内无需签证/240h免签过境</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4479,29 +4478,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>岘港</t>
+          <t>清迈</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>🇻🇳</t>
+          <t>🇹🇭</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="H43" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4509,31 +4508,31 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L43" t="n">
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N43" t="n">
         <v>4</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
         <v>7</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4545,20 +4544,20 @@
         <v>7</v>
       </c>
       <c r="V43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2月-5月</t>
+          <t>11月-2月</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>电子签</t>
+          <t>DTV 5年/教育签证</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4572,34 +4571,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>贝尔格莱德</t>
+          <t>曼谷</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>塞尔维亚</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>🇷🇸</t>
+          <t>🇹🇭</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>900</v>
+        <v>3200</v>
       </c>
       <c r="H44" t="n">
-        <v>1300</v>
+        <v>1150</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4607,13 +4606,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
         <v>7</v>
@@ -4622,41 +4621,41 @@
         <v>5</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
         <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V44" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>5月-9月</t>
+          <t>11月-2月</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>免签30天</t>
+          <t>DTV/教育签证</t>
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4670,34 +4669,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>里约</t>
+          <t>第比利斯</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>🇧🇷</t>
+          <t>🇬🇪</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="H45" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4705,56 +4704,56 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
         <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q45" t="n">
         <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V45" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>5月-8月</t>
+          <t>5月-10月</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>数字游民签</t>
+          <t>免签1年</t>
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -4768,34 +4767,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>中东</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>开普敦</t>
+          <t>阿布扎比</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>阿联酋</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>🇿🇦</t>
+          <t>🇦🇪</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="H46" t="n">
-        <v>1600</v>
+        <v>3100</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4803,43 +4802,43 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="K46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L46" t="n">
         <v>7</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O46" t="n">
         <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
         <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -4848,11 +4847,11 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>游民签/旅游</t>
+          <t>旅游签</t>
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4866,34 +4865,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中东</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>多哈</t>
+          <t>普吉</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>🇶🇦</t>
+          <t>🇹🇭</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="H47" t="n">
-        <v>2800</v>
+        <v>1250</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4901,56 +4900,56 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O47" t="n">
         <v>5</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>11月-3月</t>
+          <t>11月-4月</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>旅游签/卡星</t>
+          <t>DTV 5年</t>
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4969,29 +4968,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>吉隆坡</t>
+          <t>苏梅岛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>🇲🇾</t>
+          <t>🇹🇭</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="H48" t="n">
-        <v>1100</v>
+        <v>1350</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4999,37 +4998,37 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S48" t="n">
         <v>6</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
         <v>7</v>
@@ -5039,16 +5038,16 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>5月-8月</t>
+          <t>12月-4月</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>DE R passes</t>
+          <t>DTV 5年</t>
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -5062,34 +5061,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>伊斯坦布尔</t>
+          <t>胡志明市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>🇹🇷</t>
+          <t>🇻🇳</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="H49" t="n">
-        <v>1200</v>
+        <v>850</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5097,28 +5096,28 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L49" t="n">
         <v>8</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P49" t="n">
         <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
         <v>6</v>
@@ -5130,23 +5129,23 @@
         <v>5</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>4月-5月, 9月-10月</t>
+          <t>12月-4月</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>免签/居留</t>
+          <t>电子签/免签45天</t>
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5160,91 +5159,91 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>卡波圣卢卡斯</t>
+          <t>班斯科</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇧🇬</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H50" t="n">
         <v>900</v>
       </c>
-      <c r="H50" t="n">
-        <v>1700</v>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>美元</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U50" t="n">
         <v>6</v>
       </c>
       <c r="V50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>11月-4月</t>
+          <t>6月-9月, 12月-3月滑雪</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>临时居留</t>
+          <t>保加利亚游民签</t>
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5258,34 +5257,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>普拉亚德尔卡曼</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>希腊</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇬🇷</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="H51" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5293,7 +5292,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K51" t="n">
         <v>7</v>
@@ -5302,7 +5301,7 @@
         <v>7</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N51" t="n">
         <v>6</v>
@@ -5311,38 +5310,38 @@
         <v>6</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
         <v>7</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V51" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>11月-4月</t>
+          <t>4月-6月, 9月-10月</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>临时居留</t>
+          <t>希腊游民签</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5356,34 +5355,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>班加罗尔</t>
+          <t>圣米格尔</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>🇮🇳</t>
+          <t>🇲🇽</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="H52" t="n">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5391,56 +5390,56 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M52" t="n">
         <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>10月-2月</t>
+          <t>10月-5月</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>电子签</t>
+          <t>临时居留</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5454,34 +5453,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>宿务</t>
+          <t>弗洛里亚诺波利斯</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>菲律宾</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>🇵🇭</t>
+          <t>🇧🇷</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>1100</v>
       </c>
       <c r="H53" t="n">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5495,50 +5494,50 @@
         <v>7</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
         <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="n">
         <v>7</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
       </c>
       <c r="T53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
         <v>7</v>
       </c>
       <c r="V53" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>12月-5月</t>
+          <t>12月-3月</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>免签30天</t>
+          <t>数字游民签</t>
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5552,34 +5551,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>图卢姆</t>
+          <t>槟城</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>🇲🇽</t>
+          <t>🇲🇾</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="H54" t="n">
-        <v>1700</v>
+        <v>950</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5587,56 +5586,56 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
         <v>6</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
         <v>7</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V54" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>11月-4月</t>
+          <t>12月-2月</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>临时居留</t>
+          <t>DE R passes</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5650,34 +5649,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>利马</t>
+          <t>索菲亚</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>秘鲁</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>🇵🇪</t>
+          <t>🇧🇬</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="H55" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5685,16 +5684,16 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K55" t="n">
         <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N55" t="n">
         <v>5</v>
@@ -5703,38 +5702,38 @@
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
         <v>6</v>
       </c>
       <c r="V55" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>12月-4月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>旅游签183天</t>
+          <t>保加利亚游民签</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5748,34 +5747,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>果阿</t>
+          <t>瓦哈卡</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>🇮🇳</t>
+          <t>🇲🇽</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="H56" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5783,7 +5782,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K56" t="n">
         <v>7</v>
@@ -5795,44 +5794,44 @@
         <v>7</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P56" t="n">
         <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V56" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>11月-2月</t>
+          <t>10月-5月</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>电子签</t>
+          <t>临时居留</t>
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
@@ -5846,34 +5845,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>基加利</t>
+          <t>巴拿马城</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>卢旺达</t>
+          <t>巴拿马</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>🇷🇼</t>
+          <t>🇵🇦</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="H57" t="n">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5881,56 +5880,56 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
         <v>6</v>
       </c>
       <c r="O57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U57" t="n">
         <v>7</v>
       </c>
       <c r="V57" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>6月-9月</t>
+          <t>12月-3月</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>游民签/旅游</t>
+          <t>游民签/短租友好</t>
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
@@ -5944,34 +5943,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>卡塔赫纳</t>
+          <t>河内</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>🇨🇴</t>
+          <t>🇻🇳</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="H58" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5979,56 +5978,56 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L58" t="n">
         <v>7</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N58" t="n">
         <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V58" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>12月-3月</t>
+          <t>10月-12月</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>游民签M</t>
+          <t>电子签</t>
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -6042,34 +6041,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>内罗毕</t>
+          <t>岘港</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>肯尼亚</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>🇰🇪</t>
+          <t>🇻🇳</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H59" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6077,7 +6076,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
         <v>7</v>
@@ -6086,47 +6085,47 @@
         <v>6</v>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>5</v>
       </c>
       <c r="P59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>7月-9月, 1月-2月</t>
+          <t>2月-5月</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>游民签</t>
+          <t>电子签</t>
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
@@ -6140,69 +6139,69 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>金边</t>
+          <t>贝尔格莱德</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>塞尔维亚</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>🇰🇭</t>
+          <t>🇷🇸</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>900</v>
+      </c>
+      <c r="H60" t="n">
         <v>1300</v>
       </c>
-      <c r="H60" t="n">
-        <v>900</v>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>美元</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
         <v>7</v>
       </c>
       <c r="L60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M60" t="n">
         <v>7</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q60" t="n">
         <v>6</v>
       </c>
       <c r="R60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="n">
         <v>6</v>
@@ -6211,20 +6210,20 @@
         <v>6</v>
       </c>
       <c r="V60" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>11月-2月</t>
+          <t>5月-9月</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>E-visa/落地</t>
+          <t>免签30天</t>
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
@@ -6238,34 +6237,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>暹粒</t>
+          <t>里约</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>🇰🇭</t>
+          <t>🇧🇷</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="H61" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6273,56 +6272,56 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
         <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q61" t="n">
         <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>11月-2月</t>
+          <t>5月-8月</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>落地签</t>
+          <t>数字游民签</t>
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
@@ -6341,29 +6340,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>塔加祖特</t>
+          <t>开普敦</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>🇲🇦</t>
+          <t>🇿🇦</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="H62" t="n">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6371,56 +6370,56 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U62" t="n">
         <v>6</v>
       </c>
       <c r="V62" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>4月-10月冲浪</t>
+          <t>11月-3月</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>旅游签</t>
+          <t>游民签/旅游</t>
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
@@ -6434,34 +6433,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>亚洲</t>
+          <t>中东</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>雅加达</t>
+          <t>多哈</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>印尼</t>
+          <t>卡塔尔</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>🇮🇩</t>
+          <t>🇶🇦</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H63" t="n">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6469,25 +6468,25 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="n">
         <v>5</v>
@@ -6496,29 +6495,29 @@
         <v>4</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>6月-9月</t>
+          <t>11月-3月</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B211A</t>
+          <t>旅游签/卡星</t>
         </is>
       </c>
       <c r="Y63" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
@@ -6537,29 +6536,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>马尼拉</t>
+          <t>吉隆坡</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>菲律宾</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>🇵🇭</t>
+          <t>🇲🇾</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="H64" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6567,28 +6566,28 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
         <v>5</v>
@@ -6597,26 +6596,26 @@
         <v>6</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>12月-2月</t>
+          <t>5月-8月</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>免签30天</t>
+          <t>DE R passes</t>
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
@@ -6630,34 +6629,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>欧洲</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>安提瓜</t>
+          <t>伊斯坦布尔</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>危地马拉</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>🇬🇹</t>
+          <t>🇹🇷</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="H65" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6665,56 +6664,56 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N65" t="n">
         <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
         <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U65" t="n">
         <v>6</v>
       </c>
       <c r="V65" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>11月-4月</t>
+          <t>4月-5月, 9月-10月</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>旅游签</t>
+          <t>免签/居留</t>
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
@@ -6728,34 +6727,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>约翰内斯堡</t>
+          <t>卡波圣卢卡斯</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>🇿🇦</t>
+          <t>🇲🇽</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="H66" t="n">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6769,50 +6768,50 @@
         <v>6</v>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
         <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q66" t="n">
         <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>9月-11月, 3月-5月</t>
+          <t>11月-4月</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>游民签/旅游</t>
+          <t>临时居留</t>
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
@@ -6826,34 +6825,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>马拉喀什</t>
+          <t>普拉亚德尔卡曼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>🇲🇦</t>
+          <t>🇲🇽</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="H67" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6861,56 +6860,56 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M67" t="n">
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>3月-5月, 9月-11月</t>
+          <t>11月-4月</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>旅游签90天</t>
+          <t>临时居留</t>
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -6924,34 +6923,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>非洲</t>
+          <t>亚洲</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>开罗</t>
+          <t>班加罗尔</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>埃及</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>🇪🇬</t>
+          <t>🇮🇳</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>700</v>
+        <v>2500</v>
       </c>
       <c r="H68" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6959,19 +6958,19 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O68" t="n">
         <v>5</v>
@@ -6980,37 +6979,1605 @@
         <v>4</v>
       </c>
       <c r="Q68" t="n">
+        <v>6</v>
+      </c>
+      <c r="R68" t="n">
+        <v>5</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>6</v>
+      </c>
+      <c r="V68" t="n">
+        <v>24</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>10月-2月</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>电子签</t>
+        </is>
+      </c>
+      <c r="Y68" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>宿务</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>菲律宾</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>🇵🇭</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H69" t="n">
+        <v>900</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>7</v>
+      </c>
+      <c r="L69" t="n">
+        <v>6</v>
+      </c>
+      <c r="M69" t="n">
+        <v>7</v>
+      </c>
+      <c r="N69" t="n">
+        <v>7</v>
+      </c>
+      <c r="O69" t="n">
         <v>4</v>
       </c>
-      <c r="R68" t="n">
+      <c r="P69" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>7</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="n">
+        <v>6</v>
+      </c>
+      <c r="U69" t="n">
+        <v>7</v>
+      </c>
+      <c r="V69" t="n">
+        <v>28</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>12月-5月</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>免签30天</t>
+        </is>
+      </c>
+      <c r="Y69" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>图卢姆</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>🇲🇽</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
+      <c r="L70" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" t="n">
+        <v>6</v>
+      </c>
+      <c r="N70" t="n">
+        <v>6</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>6</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6</v>
+      </c>
+      <c r="V70" t="n">
+        <v>26</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>11月-4月</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>临时居留</t>
+        </is>
+      </c>
+      <c r="Y70" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>利马</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>🇵🇪</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>6</v>
+      </c>
+      <c r="K71" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>7</v>
+      </c>
+      <c r="M71" t="n">
+        <v>6</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>6</v>
+      </c>
+      <c r="P71" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>6</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" t="n">
+        <v>20</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>12月-4月</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>旅游签183天</t>
+        </is>
+      </c>
+      <c r="Y71" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>果阿</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>🇮🇳</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>7</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" t="n">
+        <v>7</v>
+      </c>
+      <c r="N72" t="n">
+        <v>6</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>6</v>
+      </c>
+      <c r="R72" t="n">
+        <v>5</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6</v>
+      </c>
+      <c r="V72" t="n">
+        <v>28</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>11月-2月</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>电子签</t>
+        </is>
+      </c>
+      <c r="Y72" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>基加利</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>卢旺达</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>🇷🇼</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>600</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>8</v>
+      </c>
+      <c r="N73" t="n">
+        <v>6</v>
+      </c>
+      <c r="O73" t="n">
+        <v>6</v>
+      </c>
+      <c r="P73" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>6</v>
+      </c>
+      <c r="R73" t="n">
+        <v>4</v>
+      </c>
+      <c r="S73" t="n">
+        <v>4</v>
+      </c>
+      <c r="T73" t="n">
+        <v>8</v>
+      </c>
+      <c r="U73" t="n">
+        <v>7</v>
+      </c>
+      <c r="V73" t="n">
+        <v>21</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>6月-9月</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>游民签/旅游</t>
+        </is>
+      </c>
+      <c r="Y73" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>卡塔赫纳</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>哥伦比亚</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>🇨🇴</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" t="n">
+        <v>7</v>
+      </c>
+      <c r="L74" t="n">
+        <v>7</v>
+      </c>
+      <c r="M74" t="n">
+        <v>5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="n">
+        <v>7</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>6</v>
+      </c>
+      <c r="V74" t="n">
+        <v>28</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>12月-3月</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>游民签M</t>
+        </is>
+      </c>
+      <c r="Y74" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>内罗毕</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>肯尼亚</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>🇰🇪</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7</v>
+      </c>
+      <c r="O75" t="n">
+        <v>5</v>
+      </c>
+      <c r="P75" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>6</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="n">
+        <v>5</v>
+      </c>
+      <c r="U75" t="n">
+        <v>6</v>
+      </c>
+      <c r="V75" t="n">
+        <v>22</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>7月-9月, 1月-2月</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>游民签</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>金边</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>🇰🇭</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H76" t="n">
+        <v>900</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>7</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" t="n">
+        <v>5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6</v>
+      </c>
+      <c r="R76" t="n">
+        <v>5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>6</v>
+      </c>
+      <c r="U76" t="n">
+        <v>6</v>
+      </c>
+      <c r="V76" t="n">
+        <v>28</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>11月-2月</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>E-visa/落地</t>
+        </is>
+      </c>
+      <c r="Y76" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>暹粒</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>🇰🇭</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>900</v>
+      </c>
+      <c r="H77" t="n">
+        <v>800</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>6</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5</v>
+      </c>
+      <c r="M77" t="n">
+        <v>8</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>5</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>7</v>
+      </c>
+      <c r="U77" t="n">
+        <v>7</v>
+      </c>
+      <c r="V77" t="n">
+        <v>28</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>11月-2月</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>落地签</t>
+        </is>
+      </c>
+      <c r="Y77" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>塔加祖特</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>摩洛哥</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>🇲🇦</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>700</v>
+      </c>
+      <c r="H78" t="n">
+        <v>900</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>6</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>6</v>
+      </c>
+      <c r="R78" t="n">
+        <v>5</v>
+      </c>
+      <c r="S78" t="n">
+        <v>4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>7</v>
+      </c>
+      <c r="U78" t="n">
+        <v>6</v>
+      </c>
+      <c r="V78" t="n">
+        <v>20</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>4月-10月冲浪</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>旅游签</t>
+        </is>
+      </c>
+      <c r="Y78" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>雅加达</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>印尼</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>🇮🇩</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
+        <v>6</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>6</v>
+      </c>
+      <c r="P79" t="n">
         <v>3</v>
       </c>
-      <c r="S68" t="n">
-        <v>5</v>
-      </c>
-      <c r="T68" t="n">
-        <v>5</v>
-      </c>
-      <c r="U68" t="n">
-        <v>5</v>
-      </c>
-      <c r="V68" t="n">
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>5</v>
+      </c>
+      <c r="V79" t="n">
+        <v>28</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>6月-9月</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B211A</t>
+        </is>
+      </c>
+      <c r="Y79" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>马尼拉</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>菲律宾</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>🇵🇭</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>8</v>
+      </c>
+      <c r="O80" t="n">
+        <v>5</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>5</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>6</v>
+      </c>
+      <c r="V80" t="n">
+        <v>29</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>12月-2月</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>免签30天</t>
+        </is>
+      </c>
+      <c r="Y80" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>安提瓜</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>危地马拉</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>🇬🇹</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>800</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5</v>
+      </c>
+      <c r="M81" t="n">
+        <v>6</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>6</v>
+      </c>
+      <c r="P81" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>6</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>6</v>
+      </c>
+      <c r="U81" t="n">
+        <v>6</v>
+      </c>
+      <c r="V81" t="n">
+        <v>19</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>11月-4月</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>旅游签</t>
+        </is>
+      </c>
+      <c r="Y81" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>约翰内斯堡</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>南非</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>🇿🇦</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" t="n">
+        <v>4</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8</v>
+      </c>
+      <c r="O82" t="n">
+        <v>5</v>
+      </c>
+      <c r="P82" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>6</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>5</v>
+      </c>
+      <c r="V82" t="n">
+        <v>16</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>9月-11月, 3月-5月</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>游民签/旅游</t>
+        </is>
+      </c>
+      <c r="Y82" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>马拉喀什</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>摩洛哥</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>🇲🇦</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>800</v>
+      </c>
+      <c r="H83" t="n">
+        <v>900</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>6</v>
+      </c>
+      <c r="L83" t="n">
+        <v>6</v>
+      </c>
+      <c r="M83" t="n">
+        <v>6</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4</v>
+      </c>
+      <c r="P83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
+        <v>5</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="n">
+        <v>6</v>
+      </c>
+      <c r="U83" t="n">
+        <v>5</v>
+      </c>
+      <c r="V83" t="n">
+        <v>21</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>3月-5月, 9月-11月</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>旅游签90天</t>
+        </is>
+      </c>
+      <c r="Y83" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>开罗</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>埃及</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>🇪🇬</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>700</v>
+      </c>
+      <c r="H84" t="n">
+        <v>800</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>美元</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" t="n">
+        <v>6</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>5</v>
+      </c>
+      <c r="P84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>4</v>
+      </c>
+      <c r="R84" t="n">
+        <v>3</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="n">
+        <v>5</v>
+      </c>
+      <c r="U84" t="n">
+        <v>5</v>
+      </c>
+      <c r="V84" t="n">
         <v>22</v>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>10月-4月</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>旅游签</t>
         </is>
       </c>
-      <c r="Y68" t="n">
+      <c r="Y84" t="n">
         <v>4.9</v>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -7254,25 +8821,25 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>$1000</t>
+          <t>$1,250</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>$800-$3500</t>
+          <t>$800-$3,500</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F4" s="11" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5">

--- a/data/digital-nomad-cities.xlsx
+++ b/data/digital-nomad-cities.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>免签30天</t>
+          <t>免签14-90天(依国籍)</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>6月免签/经营管理</t>
+          <t>免签15-90天(依国籍)/经营管理</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>游民友好</t>
+          <t>免签90天(多数国家)</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>旅游签/卡星</t>
+          <t>免签30天</t>
         </is>
       </c>
       <c r="Y63" t="n">

--- a/data/digital-nomad-cities.xlsx
+++ b/data/digital-nomad-cities.xlsx
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2800</v>
+        <v>16000</v>
       </c>
       <c r="H5" t="n">
         <v>2300</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2500</v>
+        <v>9600</v>
       </c>
       <c r="H16" t="n">
         <v>2400</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3500</v>
+        <v>50000</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="H33" t="n">
         <v>900</v>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5800</v>
+        <v>30000</v>
       </c>
       <c r="H37" t="n">
         <v>1400</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="H43" t="n">
         <v>850</v>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="F4" s="11" t="n">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,450</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
